--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\82107\Desktop\Main\Projects\(Website) Personal Web\kyuw0nkim.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D60DA1-5797-4AD3-A36C-8EEF58ACB3F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BFEE358-CE8E-4C57-AD7A-11BA00845B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4552" yWindow="2490" windowWidth="16200" windowHeight="9307" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="publications" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="121">
   <si>
     <t>id</t>
   </si>
@@ -374,6 +374,18 @@
   </si>
   <si>
     <t>Best Student Paper Nominee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pic.C.Understanding Productive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pic.C.When Should</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pic.C.논쟁문제 의사결정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -759,13 +771,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O17"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.7"/>
+  <sheetFormatPr defaultRowHeight="19.149999999999999" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="11.609375" customWidth="1"/>
     <col min="2" max="2" width="37.0546875" customWidth="1"/>
+    <col min="3" max="3" width="33.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -812,7 +825,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.7">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.7">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -856,10 +869,10 @@
         <v>117</v>
       </c>
       <c r="O2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.7">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -903,10 +916,10 @@
         <v>21</v>
       </c>
       <c r="O3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.7">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.7">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -949,11 +962,8 @@
       <c r="N4" t="s">
         <v>21</v>
       </c>
-      <c r="O4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.7">
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.7">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -997,10 +1007,10 @@
         <v>37</v>
       </c>
       <c r="O5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.7">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -1047,7 +1057,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.7">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.7">
       <c r="A7" t="s">
         <v>44</v>
       </c>
@@ -1094,7 +1104,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.7">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.7">
       <c r="A8" t="s">
         <v>51</v>
       </c>
@@ -1141,7 +1151,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.7">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.7">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -1188,7 +1198,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.7">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.7">
       <c r="A10" t="s">
         <v>67</v>
       </c>
@@ -1235,7 +1245,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.7">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.7">
       <c r="A11" t="s">
         <v>74</v>
       </c>
@@ -1282,7 +1292,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.7">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.7">
       <c r="A12" t="s">
         <v>80</v>
       </c>
@@ -1329,7 +1339,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.7">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.7">
       <c r="A13" t="s">
         <v>86</v>
       </c>
@@ -1376,7 +1386,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.7">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.7">
       <c r="A14" t="s">
         <v>92</v>
       </c>
@@ -1423,7 +1433,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.7">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.7">
       <c r="A15" t="s">
         <v>98</v>
       </c>
@@ -1470,7 +1480,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.7">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.7">
       <c r="A16" t="s">
         <v>105</v>
       </c>
@@ -1517,7 +1527,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="19.149999999999999" x14ac:dyDescent="0.7">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.7">
       <c r="A17" t="s">
         <v>111</v>
       </c>
@@ -1569,7 +1579,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:O1 A3:O17 A2:M2 O2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:O1 A3:N3 A2:M2 A6:O17 A4:N4 A5:N5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\82107\Desktop\Main\Projects\(Website) Personal Web\kyuw0nkim.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BFEE358-CE8E-4C57-AD7A-11BA00845B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E3F4FA5-CA5E-4A55-BA4B-5F9A0174CC07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4552" yWindow="2490" windowWidth="16200" windowHeight="9307" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -377,15 +377,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>pic.C.Understanding Productive</t>
+    <t>pic.C.When Should.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>pic.C.When Should</t>
+    <t>pic.C.Understanding Productive.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>pic.C.논쟁문제 의사결정</t>
+    <t>pic.C.논쟁문제 의사결정.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -869,7 +869,7 @@
         <v>117</v>
       </c>
       <c r="O2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.7">
@@ -916,7 +916,7 @@
         <v>21</v>
       </c>
       <c r="O3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.7">
